--- a/outputs/forecast_vacancy_rate_by_tract.xlsx
+++ b/outputs/forecast_vacancy_rate_by_tract.xlsx
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>12.27350030694875</v>
+        <v>12.94147272644794</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>12.94804637174457</v>
+        <v>13.65200997239211</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>13.65390162969897</v>
+        <v>14.36822219025688</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>0.6168417569933463</v>
+        <v>0.5427168354256302</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>0.5427167334061201</v>
+        <v>0.468594618005873</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>0.4685946214634367</v>
+        <v>0.3944724109588067</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>1.402097249040514</v>
+        <v>0.8201447473514163</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>0.8200330635152016</v>
+        <v>0.2387413088134043</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>0.2387554170279147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>1.993692323391998</v>
+        <v>1.757327827095009</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>1.756538497529562</v>
+        <v>1.524586256602922</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>1.524690254275191</v>
+        <v>1.292156679127641</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>6.64403719339091</v>
+        <v>6.479543725782477</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>6.477684065619506</v>
+        <v>6.301628964446845</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>6.301187980286092</v>
+        <v>6.122391250628956</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>3.674959518170331</v>
+        <v>2.725483828661593</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>2.79614207274052</v>
+        <v>2.096618934281145</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>2.142575933489622</v>
+        <v>1.605625037526128</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>6.320860855352396</v>
+        <v>6.504626691336371</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>6.50683985428029</v>
+        <v>6.701651560977992</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>6.702391504636531</v>
+        <v>6.900896261595229</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>4.170156879551132</v>
+        <v>4.390823633700787</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>4.262865740043292</v>
+        <v>4.442954846050531</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>4.518989786317853</v>
+        <v>4.723190879202241</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>4.965894769620465</v>
+        <v>4.133756983106938</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>4.142234223767253</v>
+        <v>3.351005296030236</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>3.354005315936629</v>
+        <v>2.577253668672713</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>3.013012476735859</v>
+        <v>1.94391135806751</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>1.946886074034037</v>
+        <v>0.9007293233752662</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>0.9012500040675407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>20.6695484927609</v>
+        <v>22.19189819012387</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>22.19189786329563</v>
+        <v>23.71425122259033</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>23.71425124734169</v>
+        <v>25.23660432931088</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>14.69702147105667</v>
+        <v>15.42250106618721</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>15.41737242357505</v>
+        <v>16.16406131625759</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>16.16489721811672</v>
+        <v>16.90812927190537</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>2.378500804355603</v>
+        <v>1.412680769742162</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>1.412680310004176</v>
+        <v>0.4468358333196232</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>0.4468358243342626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>3.523688404307741</v>
+        <v>2.891127559718852</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>2.892958687740937</v>
+        <v>2.271916240647251</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>2.272343044295603</v>
+        <v>1.653985332520707</v>
       </c>
     </row>
     <row r="77">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>4.110352266561066</v>
+        <v>4.329442997115978</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>4.320441943235473</v>
+        <v>4.49972485367692</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>4.496009360706538</v>
+        <v>4.658860231326717</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>14.72070753187816</v>
+        <v>14.94631245266522</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>14.87485599597566</v>
+        <v>14.83670537251352</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>14.79445186341774</v>
+        <v>14.60033776507448</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>14.50121022999186</v>
+        <v>14.75421716392807</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>14.70322868441573</v>
+        <v>14.97577395792181</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>14.99716900095796</v>
+        <v>15.26151588102399</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>8.097267923082013</v>
+        <v>8.539274040416471</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>8.539660360599653</v>
+        <v>8.987566419728207</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>8.987595527297955</v>
+        <v>9.435946121749188</v>
       </c>
     </row>
     <row r="97">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>16.66942869957545</v>
+        <v>16.82359384240157</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>16.79354954495734</v>
+        <v>16.93030909971242</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>16.95145708988983</v>
+        <v>17.10046832755551</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>14.86963655067955</v>
+        <v>12.27290260239396</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>15.19784310692475</v>
+        <v>15.32409981705224</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>12.58806625154185</v>
+        <v>10.16719633517935</v>
       </c>
     </row>
     <row r="107">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>37.8510136272151</v>
+        <v>42.05292927101314</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>41.96644014545972</v>
+        <v>46.12177082121136</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>46.18095409945105</v>
+        <v>50.36816220612867</v>
       </c>
     </row>
     <row r="112">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>2.239839585872836</v>
+        <v>2.075077135797645</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>2.079126663792815</v>
+        <v>1.935673777310733</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>1.936915113183417</v>
+        <v>1.799994426441872</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>3.032016663986663</v>
+        <v>1.42732481641934</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>1.46855318801999</v>
+        <v>0.0528997583026154</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>0.06884789038484011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>4.481378432230571</v>
+        <v>4.346380961335534</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>4.347602049309366</v>
+        <v>4.21139362154114</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>4.210985463416879</v>
+        <v>4.075181807373963</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>8.529898391245682</v>
+        <v>8.716357885872441</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>8.711229814884598</v>
+        <v>8.87381796817616</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>8.871886515586892</v>
+        <v>9.025483692712074</v>
       </c>
     </row>
     <row r="132">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>9.442336254850384</v>
+        <v>9.391759143242776</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>9.387808455097618</v>
+        <v>9.31352573103135</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>9.312538151710589</v>
+        <v>9.232329580857636</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>12.54515193045093</v>
+        <v>13.76426433961823</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>13.64418694615091</v>
+        <v>14.43804646564828</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>14.36014950069383</v>
+        <v>14.87813769681497</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>8.225191029371212</v>
+        <v>8.196148827885681</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>8.188913334001299</v>
+        <v>8.116692857428935</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>8.114869196029971</v>
+        <v>8.031765902775298</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>3.719347225130364</v>
+        <v>3.683753726589096</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>3.603195471366305</v>
+        <v>3.576080557379769</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>3.614346006533994</v>
+        <v>3.583203735633115</v>
       </c>
     </row>
     <row r="152">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>12.51086176302746</v>
+        <v>11.96643508096319</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>11.81391009660869</v>
+        <v>11.26098344056188</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>11.33943183464733</v>
+        <v>10.79087698241693</v>
       </c>
     </row>
     <row r="157">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>16.0805962385474</v>
+        <v>16.11750661358429</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>16.43595258265375</v>
+        <v>16.63572846690731</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>16.42179981434853</v>
+        <v>16.512164362554</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>2.0687146291686</v>
+        <v>1.097366072824348</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>1.097587577152749</v>
+        <v>0.1248079299783189</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>0.1247817498486938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>8.034799028626058</v>
+        <v>7.612580352083015</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>7.612483122501234</v>
+        <v>7.18824575453395</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>7.188240572303717</v>
+        <v>6.763895610294187</v>
       </c>
     </row>
     <row r="172">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>10.28849188160533</v>
+        <v>10.30948830788817</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>10.51146857407156</v>
+        <v>10.69949636667911</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>10.52730976505038</v>
+        <v>10.57294462058386</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>10.50486967063878</v>
+        <v>11.18388118886354</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>11.18374748940658</v>
+        <v>11.86086405861651</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>11.86085307551695</v>
+        <v>12.53781397907081</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>2.970609247969696</v>
+        <v>2.743098580869723</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>2.743181505869361</v>
+        <v>2.516264234524904</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>2.516280318313516</v>
+        <v>2.28947813954592</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>9.424703287162208</v>
+        <v>9.118228227875273</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>9.028732147341948</v>
+        <v>8.728411098544937</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>8.771671773953393</v>
+        <v>8.46837599543997</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>2.119075280779292</v>
+        <v>1.722096859641785</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>1.722520566222256</v>
+        <v>1.323963393558003</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>1.323889397234816</v>
+        <v>0.9256079385046609</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>7.718093901443066</v>
+        <v>8.284485847734494</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>7.71918225354213</v>
+        <v>7.936324964566206</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>8.345315686848902</v>
+        <v>8.815136248246009</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>2.720608186599389</v>
+        <v>1.729052132498621</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>1.729091687144175</v>
+        <v>0.7371215033710286</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>0.7371183313386046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>19.15755216926804</v>
+        <v>19.72738734031216</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>19.72955054304241</v>
+        <v>20.31289960400473</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>20.31340893232781</v>
+        <v>20.89993985266655</v>
       </c>
     </row>
     <row r="212">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>17.35545292740951</v>
+        <v>18.46204613787</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>18.40950584269075</v>
+        <v>19.56796422175295</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>19.58555299022819</v>
+        <v>20.72664861106163</v>
       </c>
     </row>
     <row r="217">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>13.17073455085626</v>
+        <v>14.00403084708318</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>13.86726294511282</v>
+        <v>12.75268777564608</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>14.37218526407472</v>
+        <v>16.35983716949492</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>7.972388220929382</v>
+        <v>6.786022583193212</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>6.682457181177561</v>
+        <v>5.454999480830304</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>5.519597612585098</v>
+        <v>4.31777077373178</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>19.40320289596033</v>
+        <v>18.8445048535155</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>18.81154203329406</v>
+        <v>18.11240053805935</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>18.09781949384014</v>
+        <v>17.33655308994557</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>17.87672939465591</v>
+        <v>18.59912276337044</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>18.59912276337044</v>
+        <v>19.32151613208497</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>19.32151613208497</v>
+        <v>20.0439095007995</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>33.57553029553307</v>
+        <v>35.29985366188081</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>35.26922989148396</v>
+        <v>37.02181218716422</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>37.03228981310564</v>
+        <v>38.77520359027189</v>
       </c>
     </row>
     <row r="242">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>16.24515113211939</v>
+        <v>15.42577854366252</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>15.37670899396078</v>
+        <v>14.59596199012221</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>14.61356756370397</v>
+        <v>13.81896215732718</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>16.02632287664274</v>
+        <v>17.06829430338076</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>16.82449578555732</v>
+        <v>17.84707272969183</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>17.97402145499577</v>
+        <v>19.00669733191473</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>19.91940183320238</v>
+        <v>20.86823094503277</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>20.86628306763959</v>
+        <v>21.7986198790356</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>21.79831866738243</v>
+        <v>22.72810517807892</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>2.520760726523083</v>
+        <v>2.66732893437624</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>2.667699432565489</v>
+        <v>2.813652748186791</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>2.813551509112143</v>
+        <v>2.959672844773399</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>6.16181438383548</v>
+        <v>5.483516721431061</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>5.483273753806262</v>
+        <v>4.803839596048435</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>4.80374885383053</v>
+        <v>4.123890244012092</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>2.034468218640908</v>
+        <v>2.139469075021286</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>2.13946874323055</v>
+        <v>2.244457286243104</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>2.244457276793567</v>
+        <v>2.34944546911631</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>3.332809312809767</v>
+        <v>3.370472753418407</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>3.409527416348851</v>
+        <v>3.451918270458467</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>3.431132948196358</v>
+        <v>3.471007820712201</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>6.493952442771604</v>
+        <v>6.775565402240394</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>6.774210916033259</v>
+        <v>7.056531109456905</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>7.057068147529868</v>
+        <v>7.339107930892306</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>5.779798807185732</v>
+        <v>6.082926150531527</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>5.984034771670757</v>
+        <v>6.340038687125254</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>6.379053811037089</v>
+        <v>6.714196595454485</v>
       </c>
     </row>
     <row r="287">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>15.8864616275372</v>
+        <v>18.15290425592593</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>16.41819386311994</v>
+        <v>16.97051748165451</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>18.68487804829265</v>
+        <v>20.93121240729751</v>
       </c>
     </row>
     <row r="292">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>5.166230653974344</v>
+        <v>4.191866740759915</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>4.186663755843462</v>
+        <v>3.219511538564863</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>3.221048124194094</v>
+        <v>2.251766093257505</v>
       </c>
     </row>
     <row r="297">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>14.68277730689312</v>
+        <v>15.71391767234067</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>16.45225032713277</v>
+        <v>18.18629797737321</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>17.48176879426151</v>
+        <v>18.54509073307063</v>
       </c>
     </row>
     <row r="302">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>25.60771644036888</v>
+        <v>24.43338827378749</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>24.37112722359606</v>
+        <v>23.20640700974135</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>23.23530760495527</v>
+        <v>22.06612753133697</v>
       </c>
     </row>
     <row r="307">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>12.69907892002251</v>
+        <v>12.13100446837287</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>12.11124475338572</v>
+        <v>11.58458472226812</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>11.58940898719473</v>
+        <v>11.0526377709432</v>
       </c>
     </row>
     <row r="312">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>23.95207772837924</v>
+        <v>25.26753634104913</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>24.85901071678169</v>
+        <v>26.21235258588967</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>26.40756424796708</v>
+        <v>27.74280381696244</v>
       </c>
     </row>
     <row r="317">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>8.803204784994428</v>
+        <v>7.163897593697289</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>7.159783392059844</v>
+        <v>5.545200150792947</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>5.545713821393552</v>
+        <v>3.928043719690418</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>12.22629726502141</v>
+        <v>11.91448230383149</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>11.91426308127892</v>
+        <v>11.60415864652855</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>11.60418101002968</v>
+        <v>11.29390207972899</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>7.234227591132583</v>
+        <v>5.076452044509075</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>5.072324490761194</v>
+        <v>2.936632867442405</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>2.93719441141702</v>
+        <v>0.7984983222995794</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>26.02771492605518</v>
+        <v>27.80196031593847</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>27.67745236111605</v>
+        <v>29.40168115073812</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>29.47958207844525</v>
+        <v>31.23510476865916</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>9.036942821249424</v>
+        <v>8.310905552390551</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>8.310892968313524</v>
+        <v>7.584779333369218</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>7.584776240295135</v>
+        <v>6.858643835125633</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>10.84616479700939</v>
+        <v>10.31253693910583</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>10.29667945141376</v>
+        <v>9.783775509496014</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>9.788570803777313</v>
+        <v>9.269399962730098</v>
       </c>
     </row>
     <row r="347">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>5.599618309750767</v>
+        <v>5.342079835501572</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>5.34207983656717</v>
+        <v>5.084541335469273</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>5.08454133543009</v>
+        <v>4.827002835319426</v>
       </c>
     </row>
     <row r="352">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>5.357417456433947</v>
+        <v>4.702317276235235</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>4.182740820064719</v>
+        <v>3.177378402006036</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>3.569254361148713</v>
+        <v>2.828067405204868</v>
       </c>
     </row>
     <row r="357">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>17.2899351505125</v>
+        <v>19.08759586157253</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>17.86603571416893</v>
+        <v>18.5648246701791</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>19.67489408784354</v>
+        <v>21.37226173177898</v>
       </c>
     </row>
     <row r="367">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>3.824055307571331</v>
+        <v>3.134074840607196</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>3.837937579032356</v>
+        <v>3.839890582047589</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>3.147758300899214</v>
+        <v>2.469309480042856</v>
       </c>
     </row>
     <row r="372">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>8.386759900752613</v>
+        <v>7.488959434881423</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>7.488959434883154</v>
+        <v>6.591158953694869</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>6.591158953694869</v>
+        <v>5.693358472508313</v>
       </c>
     </row>
     <row r="377">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>5.718826770660169</v>
+        <v>4.480503502048553</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>4.486008924312316</v>
+        <v>3.242087663607712</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>3.240262751062968</v>
+        <v>1.998197087532642</v>
       </c>
     </row>
     <row r="382">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>17.61331130943863</v>
+        <v>18.09828750564752</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>18.05252536133419</v>
+        <v>18.342233538531</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>18.3220475104754</v>
+        <v>18.52562148724768</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>6.381235870040352</v>
+        <v>5.652494110563676</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>5.663557880183962</v>
+        <v>4.905487788572874</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>4.903108915279314</v>
+        <v>4.151344846701392</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>5.44518522385395</v>
+        <v>4.839830954198298</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>4.839830925195209</v>
+        <v>4.234484606522222</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>4.234484606627251</v>
+        <v>3.629138259161234</v>
       </c>
     </row>
     <row r="397">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>2.799007126293776</v>
+        <v>2.862497546866871</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>2.862558739861816</v>
+        <v>2.925855528629814</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>2.925843679352052</v>
+        <v>2.989177962559473</v>
       </c>
     </row>
     <row r="402">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>9.010941527384468</v>
+        <v>9.371183229356696</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>9.370416417438426</v>
+        <v>9.735721330897915</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>9.735810464624791</v>
+        <v>10.10052683361976</v>
       </c>
     </row>
     <row r="407">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>6.300323604896652</v>
+        <v>6.984240838496423</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>6.251386203655215</v>
+        <v>6.672294762145525</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>6.136531738628368</v>
+        <v>4.753059615243155</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>16.67497159698848</v>
+        <v>16.58780761567395</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>15.14225144783754</v>
+        <v>14.10189378041659</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>15.18018085652137</v>
+        <v>14.85084117347357</v>
       </c>
     </row>
     <row r="417">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>24.88556542950151</v>
+        <v>23.8719135666394</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>23.85785417711867</v>
+        <v>22.89148493250617</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>22.89410645466354</v>
+        <v>21.91892086484506</v>
       </c>
     </row>
     <row r="422">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>11.0630336759634</v>
+        <v>9.512939188704753</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>9.512678368487036</v>
+        <v>7.958701283765503</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>7.958681043344273</v>
+        <v>6.404402657562564</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>16.60779884183608</v>
+        <v>16.20402324475888</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>16.06512434119701</v>
+        <v>15.57356757498187</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>15.67510029135449</v>
+        <v>15.24771005432271</v>
       </c>
     </row>
     <row r="432">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>25.95946976247142</v>
+        <v>27.08095929872047</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>25.65982893106515</v>
+        <v>25.80297474398369</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>26.88650556047996</v>
+        <v>27.77558263873575</v>
       </c>
     </row>
     <row r="437">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>27.19340879999785</v>
+        <v>29.41148458403334</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>29.3713205046171</v>
+        <v>31.39355497253506</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>31.3795898683576</v>
+        <v>33.3337300485044</v>
       </c>
     </row>
     <row r="442">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>7.458733904355711</v>
+        <v>7.758065583504527</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>7.687813288105766</v>
+        <v>7.741759898142896</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>7.694702666061908</v>
+        <v>7.584282516538303</v>
       </c>
     </row>
     <row r="447">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>6.920139007112438</v>
+        <v>6.974025834433816</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>6.982351053709521</v>
+        <v>7.027100611287935</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>7.024412924767002</v>
+        <v>7.072112328579253</v>
       </c>
     </row>
     <row r="452">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>6.093588145073832</v>
+        <v>6.421500124769592</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>5.427104298707918</v>
+        <v>4.947385857318807</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>5.784547654459327</v>
+        <v>5.984756981289579</v>
       </c>
     </row>
     <row r="457">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>10.07558473111786</v>
+        <v>10.01763151950005</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>10.40720855893847</v>
+        <v>10.54695278783657</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>10.28593543994726</v>
+        <v>10.29322201250516</v>
       </c>
     </row>
     <row r="462">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>2.397292989844553</v>
+        <v>1.649026184865646</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>1.65504436452954</v>
+        <v>0.9334185163192128</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>0.9358984536549553</v>
+        <v>0.2252506597800075</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>15.98871377010314</v>
+        <v>16.63764722175243</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>16.63667179699764</v>
+        <v>17.29422202329423</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>17.29431205804926</v>
+        <v>17.95106692910113</v>
       </c>
     </row>
     <row r="472">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>2.895085567953881</v>
+        <v>1.712398049527708</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>1.713096227448923</v>
+        <v>0.5287170112459592</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>0.5285591602272343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>25.02192026695531</v>
+        <v>24.97816802818917</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>24.99473515730879</v>
+        <v>24.9259584524462</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>24.92123913010202</v>
+        <v>24.8595909096707</v>
       </c>
     </row>
     <row r="482">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>18.0836745739891</v>
+        <v>17.23255150499647</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>17.25562428769301</v>
+        <v>16.48973003549922</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>16.50335104404417</v>
+        <v>15.78777159163683</v>
       </c>
     </row>
     <row r="487">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>19.62325556019113</v>
+        <v>18.15415468315215</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>18.15472764450541</v>
+        <v>16.68545588150981</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>16.68520657823476</v>
+        <v>15.21600917004233</v>
       </c>
     </row>
     <row r="492">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>12.48060175059842</v>
+        <v>11.60563156010553</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>11.60257812649537</v>
+        <v>10.71050846236677</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>10.70966030530016</v>
+        <v>9.812840893428181</v>
       </c>
     </row>
     <row r="497">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>20.74954212937552</v>
+        <v>19.8257164540872</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>19.8269493028898</v>
+        <v>18.89272668731618</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>18.89260852211686</v>
+        <v>17.95938242494721</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>10.6585806773053</v>
+        <v>10.11731335358669</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>10.1172512755061</v>
+        <v>9.574670420688232</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>9.574667180592982</v>
+        <v>9.032017767504023</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>11.03082201317285</v>
+        <v>9.316464450566471</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>9.316633575094805</v>
+        <v>7.604345194402129</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>7.604361719078962</v>
+        <v>5.892275512268288</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>26.41165255937324</v>
+        <v>26.92653350202199</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>26.93642562471617</v>
+        <v>27.49747506812342</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>27.50118387438018</v>
+        <v>28.07954305299513</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>10.37100634188224</v>
+        <v>7.745065201184516</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>6.329564902631641</v>
+        <v>2.433700221551305</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>3.717199384244225</v>
+        <v>0.9728327299968527</v>
       </c>
     </row>
     <row r="522">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>38.66635411072756</v>
+        <v>39.36141783858756</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>39.36023545590992</v>
+        <v>40.04307486602261</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>40.04293307167527</v>
+        <v>40.72430651041566</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>10.04329009440089</v>
+        <v>6.35503681375279</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>6.355041136461847</v>
+        <v>2.66713055180373</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>2.667130607740809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>13.30852399357658</v>
+        <v>11.54624105828994</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>11.56162572283785</v>
+        <v>9.766152461872956</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>9.762451880559817</v>
+        <v>7.974962121516558</v>
       </c>
     </row>
     <row r="537">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>12.92486939474884</v>
+        <v>8.203649427130294</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>8.344557897733303</v>
+        <v>4.069031225009223</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>4.190190847131565</v>
+        <v>0.2978918892551832</v>
       </c>
     </row>
     <row r="542">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>14.0093768257585</v>
+        <v>14.57571193207491</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>14.11069170257791</v>
+        <v>14.60521920290542</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>14.8571832393371</v>
+        <v>15.39061858303097</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>31.42608009137712</v>
+        <v>31.32989113098147</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>31.32994778391174</v>
+        <v>31.23440995439479</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>31.23441592205044</v>
+        <v>31.13894668077507</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>15.33079003959018</v>
+        <v>13.94105521132597</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>13.94418410276835</v>
+        <v>12.57933009416188</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>12.57985578509927</v>
+        <v>11.21918204980996</v>
       </c>
     </row>
     <row r="557">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>11.90511503113485</v>
+        <v>11.97774255876785</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>11.9759754151138</v>
+        <v>12.05535099646399</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>12.05565470129992</v>
+        <v>12.13387054866791</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>20.46806191860772</v>
+        <v>18.63561049082488</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>18.60393036792691</v>
+        <v>16.81907473597503</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>16.8281200315003</v>
+        <v>15.02967486770101</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>21.07118397057906</v>
+        <v>20.10743374767745</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>20.10749010087009</v>
+        <v>19.14476026505902</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>19.1447637637368</v>
+        <v>18.18209727847394</v>
       </c>
     </row>
     <row r="572">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>13.1063405263466</v>
+        <v>10.57662328092083</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>10.57994843841008</v>
+        <v>8.039020910203725</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>8.038401856324487</v>
+        <v>5.499561377848899</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>23.27718426984126</v>
+        <v>24.59036023563854</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>24.58143527109831</v>
+        <v>25.8575464714454</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>25.85340097728082</v>
+        <v>27.11229622475851</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>2.511022918162346</v>
+        <v>1.961641960577355</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>2.162143679960477</v>
+        <v>2.895558024790759</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>2.12706126846299</v>
+        <v>1.523983820020856</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>24.94040314330602</v>
+        <v>24.788939266159</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>24.78893164661309</v>
+        <v>24.63713726528912</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>24.63713708113463</v>
+        <v>24.48533471195578</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>12.54117578420525</v>
+        <v>12.93781259958725</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>12.92753421332142</v>
+        <v>13.32305535247904</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>13.32848947113983</v>
+        <v>13.7246004613532</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>18.39105567322221</v>
+        <v>18.18588122427052</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>18.40498589842625</v>
+        <v>18.25578447471584</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>18.13018976971426</v>
+        <v>17.94890361015642</v>
       </c>
     </row>
     <row r="602">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>23.2756612209578</v>
+        <v>23.20247242575138</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>23.2026344611887</v>
+        <v>23.12679908847588</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>23.12679025017543</v>
+        <v>23.05109923629901</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>21.25692478878063</v>
+        <v>19.75269125817578</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>19.79241950396547</v>
+        <v>18.24362819261141</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>18.23090116140855</v>
+        <v>16.69638403343846</v>
       </c>
     </row>
     <row r="612">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>26.12700412981452</v>
+        <v>25.01361980443092</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>25.02289951835753</v>
+        <v>23.98579385366898</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>23.98728578428413</v>
+        <v>22.9624436947525</v>
       </c>
     </row>
     <row r="617">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>8.075751013567395</v>
+        <v>6.041924974057036</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>6.080838589743216</v>
+        <v>4.040049279026714</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>4.022190327378567</v>
+        <v>1.984596729051951</v>
       </c>
     </row>
     <row r="622">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>29.32306547531549</v>
+        <v>28.35983694679099</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>28.34577661055529</v>
+        <v>27.4199904476564</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>27.42300576025934</v>
+        <v>26.48918988633063</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>13.19887811007456</v>
+        <v>11.59948263926753</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>11.60170319832613</v>
+        <v>10.01589534192344</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>10.01643444262145</v>
+        <v>8.433925346673362</v>
       </c>
     </row>
     <row r="632">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>7.724965386805135</v>
+        <v>5.938554301232713</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>5.93648553409334</v>
+        <v>4.130478270633112</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>4.130201415975926</v>
+        <v>2.321571676061954</v>
       </c>
     </row>
     <row r="637">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>26.40968359574451</v>
+        <v>27.2007780791132</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>27.20069384709457</v>
+        <v>27.98972202857676</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>27.98971829009459</v>
+        <v>28.77865476259381</v>
       </c>
     </row>
     <row r="642">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>8.775376166674649</v>
+        <v>8.442242755875224</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>7.585498008478306</v>
+        <v>6.566841936990023</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>7.280884003173306</v>
+        <v>6.833567316654673</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>12.42037259812226</v>
+        <v>10.60977275900817</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>10.54929348062349</v>
+        <v>8.488049788031869</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>8.459845024602423</v>
+        <v>6.281712526767233</v>
       </c>
     </row>
     <row r="652">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>20.49229527476799</v>
+        <v>19.48217847652439</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>19.48310851292264</v>
+        <v>18.46441132179624</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>18.46432847417923</v>
+        <v>17.44639562421705</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>11.1805182202807</v>
+        <v>8.346698587548175</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>8.425070548746621</v>
+        <v>5.909561301081137</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>5.947577633187329</v>
+        <v>3.586473010932675</v>
       </c>
     </row>
     <row r="662">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>15.17301880434895</v>
+        <v>15.48003120514744</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>15.54312347800349</v>
+        <v>15.83095203353798</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>15.80356894931029</v>
+        <v>16.09972360924544</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>12.78303368236987</v>
+        <v>11.68608419619569</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>11.68557738290288</v>
+        <v>10.58446845667568</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>10.58438680539011</v>
+        <v>9.482607763298962</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>27.60700464734916</v>
+        <v>27.73659516422745</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>27.7568620793854</v>
+        <v>28.01276409082305</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>28.01755260836596</v>
+        <v>28.30329857004739</v>
       </c>
     </row>
     <row r="677">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>22.53709410954876</v>
+        <v>22.37665375555962</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>22.44435199139422</v>
+        <v>22.55771738747189</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>22.5908296989309</v>
+        <v>22.83811795376119</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>21.87692913552218</v>
+        <v>19.8537976782341</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>19.361057957212</v>
+        <v>17.30386783050623</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>17.55905716382579</v>
+        <v>15.51950598273703</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>22.29241792811045</v>
+        <v>23.16241524743912</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>23.16597102301406</v>
+        <v>24.0599948770216</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>24.06074235276804</v>
+        <v>24.95981693384341</v>
       </c>
     </row>
     <row r="692">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>12.92734061144552</v>
+        <v>12.42234712439791</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>12.42337778035796</v>
+        <v>11.90972290640185</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>11.90962384069787</v>
+        <v>11.39680149129386</v>
       </c>
     </row>
     <row r="697">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>10.05110618881416</v>
+        <v>10.20101548093351</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>10.20009014750063</v>
+        <v>10.3550374492677</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>10.35516174628764</v>
+        <v>10.50943230866173</v>
       </c>
     </row>
     <row r="702">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>20.84041700427872</v>
+        <v>21.74797458856831</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>20.94984604056555</v>
+        <v>21.10994654482722</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>21.86042859848662</v>
+        <v>22.72336466206432</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>32.03592025255789</v>
+        <v>35.96041935678814</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>32.70959737290081</v>
+        <v>33.46884759660565</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>36.63629128794557</v>
+        <v>40.47960691044294</v>
       </c>
     </row>
     <row r="712">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>24.71628557866948</v>
+        <v>24.59958293681007</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>24.55789744188139</v>
+        <v>24.51905418857955</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>24.52983181314715</v>
+        <v>24.47085831405185</v>
       </c>
     </row>
     <row r="717">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>15.11685260890435</v>
+        <v>13.28384872006382</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>13.40655214434028</v>
+        <v>12.00635167950181</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>12.08669535863834</v>
+        <v>10.96988567634938</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>11.75935823386759</v>
+        <v>10.32794907357208</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>10.29042492173822</v>
+        <v>8.874605950655891</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>8.890140873248889</v>
+        <v>7.467867595518694</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>21.88095135082644</v>
+        <v>21.65509155129066</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>21.7045211638406</v>
+        <v>21.43579913796744</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>21.41855907605685</v>
+        <v>21.16478653891245</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>15.06630004664807</v>
+        <v>13.8317817532376</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>13.86830603170536</v>
+        <v>12.63298795951653</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>12.61492359957267</v>
+        <v>11.38000108596389</v>
       </c>
     </row>
     <row r="737">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>31.75234862542517</v>
+        <v>32.75656116257495</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>32.75648839845368</v>
+        <v>33.75892640981233</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>33.75892315958194</v>
+        <v>34.76128190635853</v>
       </c>
     </row>
     <row r="742">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>6.439850612404384</v>
+        <v>5.814652974375087</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>5.814315934103946</v>
+        <v>5.183899846710778</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>5.183874849588222</v>
+        <v>4.553071727678804</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>12.80929388783904</v>
+        <v>11.12962191845914</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>11.12520248369466</v>
+        <v>9.467786199119661</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>9.468414328515816</v>
+        <v>7.807834867968651</v>
       </c>
     </row>
     <row r="752">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>6.031443780299719</v>
+        <v>5.077008104789677</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>5.084221436265702</v>
+        <v>4.116856025266719</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>4.114954014989479</v>
+        <v>3.150997914912042</v>
       </c>
     </row>
     <row r="757">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>29.16138165223457</v>
+        <v>30.96718726565138</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>30.95338657197771</v>
+        <v>32.75461179544159</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>32.76288507494427</v>
+        <v>34.56685616373985</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>2.317906995987025</v>
+        <v>1.561502033582448</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>1.549964838964194</v>
+        <v>0.795210635980661</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>0.8005940964201924</v>
+        <v>0.04506961969746826</v>
       </c>
     </row>
     <row r="767">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>14.64921155852897</v>
+        <v>15.34341373024415</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>15.34385187128975</v>
+        <v>16.04171771799</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>16.04178658792803</v>
+        <v>16.74022831554993</v>
       </c>
     </row>
     <row r="772">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>7.132405855470779</v>
+        <v>7.31721913298915</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>7.327510473146056</v>
+        <v>7.495098251234703</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>7.492296961065656</v>
+        <v>7.664573498973115</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>5.722963019443166</v>
+        <v>6.022938267436653</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>6.061088269686725</v>
+        <v>6.491011619291837</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>6.518140683509269</v>
+        <v>7.040472163799315</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>5.957994450820806</v>
+        <v>5.157867313627557</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>5.157728644456196</v>
+        <v>4.355073023279949</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>4.355064481345237</v>
+        <v>3.552253107128207</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>22.50110882774871</v>
+        <v>22.61992248918634</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>22.61032395142298</v>
+        <v>22.66119435727979</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>22.65930432349473</v>
+        <v>22.69679612401807</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>0.7919744324347743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="795">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>4.484393365122521</v>
+        <v>3.061330322917723</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>3.061239020886335</v>
+        <v>1.638679570851</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>1.638691719068294</v>
+        <v>0.2160652634361604</v>
       </c>
     </row>
     <row r="802">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>10.70565834000732</v>
+        <v>11.03485747212381</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>10.37372076817186</v>
+        <v>10.19512920149637</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>10.73179098255376</v>
+        <v>10.96538627404109</v>
       </c>
     </row>
     <row r="807">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>2.650267080394551</v>
+        <v>1.464789226593219</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>1.618778641367801</v>
+        <v>0.5356964007388019</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>0.4203526470971948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="812">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>2.559893746759303</v>
+        <v>2.175000507336733</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>2.173886706375293</v>
+        <v>1.78912027951463</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>1.789647184437158</v>
+        <v>1.404820766460111</v>
       </c>
     </row>
     <row r="817">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>7.854320156595716</v>
+        <v>7.951177515633685</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>8.181052382256762</v>
+        <v>8.503004483975895</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>8.27781236605952</v>
+        <v>8.379255098568976</v>
       </c>
     </row>
     <row r="822">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>0.9474626828428127</v>
+        <v>0.509724958409242</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>0.6180566183680485</v>
+        <v>0.2774728157360631</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>0.1792734378257448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>12.02779048427326</v>
+        <v>11.99359559045252</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>11.99383869094966</v>
+        <v>11.95906323255856</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>11.95900783345901</v>
+        <v>11.92436467736596</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>10.35278618821783</v>
+        <v>9.876353181354894</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>9.85143059736156</v>
+        <v>9.369605109943915</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>9.383578060260037</v>
+        <v>8.9047758894813</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>4.973318494518116</v>
+        <v>5.028212339395005</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>5.028212342138292</v>
+        <v>5.083106224282707</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>5.083106224519504</v>
+        <v>5.138000109880799</v>
       </c>
     </row>
     <row r="842">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>7.645960682278045</v>
+        <v>6.983689114834009</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>7.010490778689227</v>
+        <v>6.316004626437065</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>6.307634238899933</v>
+        <v>5.623208975428724</v>
       </c>
     </row>
     <row r="847">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>36.01726794424207</v>
+        <v>38.08018941954626</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>38.08017852791034</v>
+        <v>40.14302014257921</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>40.14301809999797</v>
+        <v>42.20584473786845</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>23.70448269681205</v>
+        <v>21.55153330061804</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>21.16390519057559</v>
+        <v>19.07513966696769</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>19.25413463397836</v>
+        <v>17.13573093434935</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>12.28004341356681</v>
+        <v>12.24432851599901</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>12.24107269272009</v>
+        <v>12.17650984860974</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>12.17603526753629</v>
+        <v>12.10726743800012</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>3.826964037363479</v>
+        <v>3.623567190075419</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>3.623717515736795</v>
+        <v>3.423407053306624</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>3.423415165282943</v>
+        <v>3.223271252466785</v>
       </c>
     </row>
     <row r="867">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>10.04877364961023</v>
+        <v>10.03578002348501</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>9.944543942721275</v>
+        <v>10.01824188776008</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>10.04916738559699</v>
+        <v>10.09348024554589</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>17.27998905187836</v>
+        <v>18.05465214448407</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>18.08043662465315</v>
+        <v>18.81577077338113</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>18.80845663975699</v>
+        <v>19.55494700140576</v>
       </c>
     </row>
     <row r="877">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>19.26778486272501</v>
+        <v>19.8104022737957</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>19.81040189410682</v>
+        <v>20.35299256065587</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>20.35299255510795</v>
+        <v>20.89558283087226</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>11.20181710726601</v>
+        <v>11.49159281438341</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>11.4916005469221</v>
+        <v>11.78116854159094</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>11.78116827367797</v>
+        <v>12.07074346505956</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>2.878558091947407</v>
+        <v>2.015236563310083</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>2.025677553245681</v>
+        <v>1.145065330810539</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>1.142209511179447</v>
+        <v>0.2663266394177182</v>
       </c>
     </row>
     <row r="892">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>22.72341801584102</v>
+        <v>24.05531654344878</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>24.05527739579099</v>
+        <v>25.3869434913284</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>25.38693354860506</v>
+        <v>26.71854061103799</v>
       </c>
     </row>
     <row r="897">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>4.806806686659725</v>
+        <v>4.315351773313333</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>4.316082229914016</v>
+        <v>3.821693440101679</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>3.821572031141098</v>
+        <v>3.327670880008282</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>7.374431187718617</v>
+        <v>7.610340058629486</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>7.527165681861368</v>
+        <v>7.699721492112144</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>7.766889125608081</v>
+        <v>7.990605826082612</v>
       </c>
     </row>
     <row r="907">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>7.29428823821272</v>
+        <v>7.426364938397025</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>7.42810456186798</v>
+        <v>7.555773542924211</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>7.555389835197584</v>
+        <v>7.684031024271516</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>14.75885135624482</v>
+        <v>15.62217322317893</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>15.62193804825433</v>
+        <v>16.48540734580533</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>16.48549687153203</v>
+        <v>17.34891004561181</v>
       </c>
     </row>
     <row r="917">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>15.62084512908074</v>
+        <v>17.0152848447589</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>17.01454793172176</v>
+        <v>18.4018357928757</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>18.40174015390012</v>
+        <v>19.78809982406576</v>
       </c>
     </row>
     <row r="922">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>15.30544577392843</v>
+        <v>15.14530231138427</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>15.14530567120848</v>
+        <v>14.98499834988022</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>14.98499828370293</v>
+        <v>14.8246941898443</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>4.027588712421347</v>
+        <v>2.861742319135249</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>2.856419609471721</v>
+        <v>1.663613998692867</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>1.661877356013189</v>
+        <v>0.4602757502114514</v>
       </c>
     </row>
     <row r="932">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>2.530648944715615</v>
+        <v>2.03311192793964</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>2.033055808744708</v>
+        <v>1.536638583252639</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>1.53664113949305</v>
+        <v>1.040172907286872</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>3.801916645012634</v>
+        <v>3.937567154850804</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>3.938469409126121</v>
+        <v>4.077792544439892</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>4.078228310941681</v>
+        <v>4.219325233534349</v>
       </c>
     </row>
     <row r="942">
@@ -12747,7 +12747,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>18.89510621283086</v>
+        <v>17.39280243503928</v>
       </c>
     </row>
     <row r="955">
@@ -12760,7 +12760,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>17.39857940669872</v>
+        <v>15.92664363077282</v>
       </c>
     </row>
     <row r="956">
@@ -12773,7 +12773,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>15.92841748522698</v>
+        <v>14.46580638986884</v>
       </c>
     </row>
     <row r="957">
@@ -12812,7 +12812,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>10.49303412798233</v>
+        <v>10.78193635526411</v>
       </c>
     </row>
     <row r="960">
@@ -12825,7 +12825,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>10.86769664574097</v>
+        <v>11.22895789487437</v>
       </c>
     </row>
     <row r="961">
@@ -12838,7 +12838,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>11.15478774780052</v>
+        <v>11.45346899326307</v>
       </c>
     </row>
     <row r="962">
@@ -12877,7 +12877,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>13.30818105851291</v>
+        <v>11.61384326334716</v>
       </c>
     </row>
     <row r="965">
@@ -12890,7 +12890,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>11.61795124463761</v>
+        <v>9.956743107333541</v>
       </c>
     </row>
     <row r="966">
@@ -12903,7 +12903,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>9.957420466115227</v>
+        <v>8.301675027664977</v>
       </c>
     </row>
     <row r="967">
@@ -12942,7 +12942,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>32.82600532140615</v>
+        <v>35.67404402677766</v>
       </c>
     </row>
     <row r="970">
@@ -12955,7 +12955,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>35.70583236842625</v>
+        <v>38.57778747083159</v>
       </c>
     </row>
     <row r="971">
@@ -12968,7 +12968,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>38.55230861629036</v>
+        <v>41.40509435126183</v>
       </c>
     </row>
     <row r="972">
@@ -13007,7 +13007,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>9.814883543961905</v>
+        <v>9.04163001124725</v>
       </c>
     </row>
     <row r="975">
@@ -13020,7 +13020,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>9.714644199722841</v>
+        <v>9.230218078585619</v>
       </c>
     </row>
     <row r="976">
@@ -13033,7 +13033,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>8.801777211877434</v>
+        <v>8.133483545799432</v>
       </c>
     </row>
     <row r="977">
@@ -13072,7 +13072,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>14.85940286888106</v>
+        <v>14.04821558243252</v>
       </c>
     </row>
     <row r="980">
@@ -13085,7 +13085,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>14.04843033065135</v>
+        <v>13.23593902757209</v>
       </c>
     </row>
     <row r="981">
@@ -13098,7 +13098,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>13.23591242448594</v>
+        <v>12.42358266345322</v>
       </c>
     </row>
     <row r="982">
@@ -13137,7 +13137,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>36.32022138341265</v>
+        <v>40.50739224123919</v>
       </c>
     </row>
     <row r="985">
@@ -13150,7 +13150,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>40.50739224123948</v>
+        <v>44.69456309412067</v>
       </c>
     </row>
     <row r="986">
@@ -13163,7 +13163,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>44.69456309412067</v>
+        <v>48.88173394700215</v>
       </c>
     </row>
   </sheetData>
